--- a/data/contributors.xlsx
+++ b/data/contributors.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="243">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -740,6 +740,15 @@
   </si>
   <si>
     <t xml:space="preserve">take_hold_catch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expression of the sense ‘maize’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">August 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maize</t>
   </si>
 </sst>
 </file>
@@ -4499,7 +4508,7 @@
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -4542,20 +4551,42 @@
       <c r="T73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
+      <c r="K74" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+      <c r="N74" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>

--- a/data/contributors.xlsx
+++ b/data/contributors.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="246">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -749,6 +749,15 @@
   </si>
   <si>
     <t xml:space="preserve">maize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meaning of words hajwan and dʒanawar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dasha Tsikh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hajwan_and_janawar</t>
   </si>
 </sst>
 </file>
@@ -843,7 +852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -877,6 +886,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4595,20 +4608,42 @@
       <c r="T74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
+      <c r="K75" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
+      <c r="N75" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>

--- a/data/contributors.xlsx
+++ b/data/contributors.xlsx
@@ -751,7 +751,7 @@
     <t xml:space="preserve">maize</t>
   </si>
   <si>
-    <t xml:space="preserve">Meaning of words hajwan and dʒanawar</t>
+    <t xml:space="preserve">Meaning of words hajwan and janawar</t>
   </si>
   <si>
     <t xml:space="preserve">Dasha Tsikh</t>
@@ -852,7 +852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -886,10 +886,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4614,7 +4610,7 @@
       <c r="B75" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="8" t="s">
         <v>243</v>
       </c>
       <c r="D75" s="2" t="s">
